--- a/IM1000.xlsx
+++ b/IM1000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I872"/>
+  <dimension ref="A1:I873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>6070.6</v>
       </c>
       <c r="H339" t="n">
-        <v>7299891.776</v>
+        <v>7299891.775999999</v>
       </c>
       <c r="I339" t="n">
         <v>60774</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>5517.4</v>
       </c>
       <c r="H399" t="n">
-        <v>8853571.963999998</v>
+        <v>8853571.963999996</v>
       </c>
       <c r="I399" t="n">
         <v>80318</v>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>5279</v>
       </c>
       <c r="H448" t="n">
-        <v>8158920.72</v>
+        <v>8158920.719999999</v>
       </c>
       <c r="I448" t="n">
         <v>76924</v>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>5284</v>
       </c>
       <c r="H449" t="n">
-        <v>8852218.816</v>
+        <v>8852218.815999998</v>
       </c>
       <c r="I449" t="n">
         <v>83508</v>
@@ -15261,7 +15261,7 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>4808.4</v>
       </c>
       <c r="H467" t="n">
-        <v>8731958.507999999</v>
+        <v>8731958.507999998</v>
       </c>
       <c r="I467" t="n">
         <v>90594</v>
@@ -15855,7 +15855,7 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>4606.2</v>
       </c>
       <c r="H505" t="n">
-        <v>8356151.736</v>
+        <v>8356151.735999999</v>
       </c>
       <c r="I505" t="n">
         <v>90140</v>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>4622.8</v>
       </c>
       <c r="H506" t="n">
-        <v>7431430.208</v>
+        <v>7431430.207999999</v>
       </c>
       <c r="I506" t="n">
         <v>80063</v>
@@ -17142,7 +17142,7 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>4457.4</v>
       </c>
       <c r="H521" t="n">
-        <v>7688870.464</v>
+        <v>7688870.463999999</v>
       </c>
       <c r="I521" t="n">
         <v>85871</v>
@@ -17637,7 +17637,7 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>4405</v>
       </c>
       <c r="H526" t="n">
-        <v>7954040.952</v>
+        <v>7954040.951999999</v>
       </c>
       <c r="I526" t="n">
         <v>90715</v>
@@ -17802,7 +17802,7 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -29216,6 +29216,39 @@
       </c>
       <c r="I872" t="n">
         <v>100970</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>0</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>IMZL.CFE</t>
+        </is>
+      </c>
+      <c r="D873" t="n">
+        <v>8480</v>
+      </c>
+      <c r="E873" t="n">
+        <v>8514.6</v>
+      </c>
+      <c r="F873" t="n">
+        <v>8338</v>
+      </c>
+      <c r="G873" t="n">
+        <v>8531.4</v>
+      </c>
+      <c r="H873" t="n">
+        <v>239709047800</v>
+      </c>
+      <c r="I873" t="n">
+        <v>142245</v>
       </c>
     </row>
   </sheetData>

--- a/IM1000.xlsx
+++ b/IM1000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I873"/>
+  <dimension ref="A1:I874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>5279</v>
       </c>
       <c r="H448" t="n">
-        <v>8158920.719999999</v>
+        <v>8158920.72</v>
       </c>
       <c r="I448" t="n">
         <v>76924</v>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>5284</v>
       </c>
       <c r="H449" t="n">
-        <v>8852218.815999998</v>
+        <v>8852218.815999996</v>
       </c>
       <c r="I449" t="n">
         <v>83508</v>
@@ -15261,7 +15261,7 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>4457.4</v>
       </c>
       <c r="H521" t="n">
-        <v>7688870.463999999</v>
+        <v>7688870.464</v>
       </c>
       <c r="I521" t="n">
         <v>85871</v>
@@ -17637,7 +17637,7 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -29249,6 +29249,39 @@
       </c>
       <c r="I873" t="n">
         <v>142245</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>0</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>IMZL.CFE</t>
+        </is>
+      </c>
+      <c r="D874" t="n">
+        <v>8445</v>
+      </c>
+      <c r="E874" t="n">
+        <v>8479.4</v>
+      </c>
+      <c r="F874" t="n">
+        <v>8110.2</v>
+      </c>
+      <c r="G874" t="n">
+        <v>8423.799999999999</v>
+      </c>
+      <c r="H874" t="n">
+        <v>271218487200</v>
+      </c>
+      <c r="I874" t="n">
+        <v>164108</v>
       </c>
     </row>
   </sheetData>

--- a/IM1000.xlsx
+++ b/IM1000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I874"/>
+  <dimension ref="A1:I875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>6070.6</v>
       </c>
       <c r="H339" t="n">
-        <v>7299891.775999999</v>
+        <v>7299891.776</v>
       </c>
       <c r="I339" t="n">
         <v>60774</v>
@@ -11631,7 +11631,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>5517.4</v>
       </c>
       <c r="H399" t="n">
-        <v>8853571.963999996</v>
+        <v>8853571.964</v>
       </c>
       <c r="I399" t="n">
         <v>80318</v>
@@ -13611,7 +13611,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>5284</v>
       </c>
       <c r="H449" t="n">
-        <v>8852218.815999996</v>
+        <v>8852218.816</v>
       </c>
       <c r="I449" t="n">
         <v>83508</v>
@@ -15261,7 +15261,7 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>5209.6</v>
       </c>
       <c r="H454" t="n">
-        <v>7449531.196</v>
+        <v>7449531.196000001</v>
       </c>
       <c r="I454" t="n">
         <v>70893</v>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>4808.4</v>
       </c>
       <c r="H467" t="n">
-        <v>8731958.507999998</v>
+        <v>8731958.507999999</v>
       </c>
       <c r="I467" t="n">
         <v>90594</v>
@@ -15855,7 +15855,7 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>4881.4</v>
       </c>
       <c r="H479" t="n">
-        <v>8722512.927999998</v>
+        <v>8722512.927999999</v>
       </c>
       <c r="I479" t="n">
         <v>89853</v>
@@ -16251,7 +16251,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>4606.2</v>
       </c>
       <c r="H505" t="n">
-        <v>8356151.735999999</v>
+        <v>8356151.736</v>
       </c>
       <c r="I505" t="n">
         <v>90140</v>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>4622.8</v>
       </c>
       <c r="H506" t="n">
-        <v>7431430.207999999</v>
+        <v>7431430.208</v>
       </c>
       <c r="I506" t="n">
         <v>80063</v>
@@ -17142,7 +17142,7 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>4515.6</v>
       </c>
       <c r="H516" t="n">
-        <v>8216291.411999999</v>
+        <v>8216291.412</v>
       </c>
       <c r="I516" t="n">
         <v>89892</v>
@@ -17472,7 +17472,7 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>4577.2</v>
       </c>
       <c r="H519" t="n">
-        <v>8051276.423999999</v>
+        <v>8051276.424</v>
       </c>
       <c r="I519" t="n">
         <v>88060</v>
@@ -17571,7 +17571,7 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>4474.8</v>
       </c>
       <c r="H523" t="n">
-        <v>7706823.343999999</v>
+        <v>7706823.344</v>
       </c>
       <c r="I523" t="n">
         <v>86309</v>
@@ -17703,7 +17703,7 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>4405</v>
       </c>
       <c r="H526" t="n">
-        <v>7954040.951999999</v>
+        <v>7954040.952</v>
       </c>
       <c r="I526" t="n">
         <v>90715</v>
@@ -17802,7 +17802,7 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B698" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B700" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B701" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B704" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B705" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B706" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B707" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B708" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B709" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B710" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B711" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B712" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B715" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B716" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B717" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B718" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B719" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B720" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B722" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>6302.2</v>
       </c>
       <c r="H722" t="n">
-        <v>8984406.019999998</v>
+        <v>8984406.02</v>
       </c>
       <c r="I722" t="n">
         <v>71184</v>
@@ -24270,7 +24270,7 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B725" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -26481,7 +26481,7 @@
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -28824,7 +28824,7 @@
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -29242,10 +29242,10 @@
         <v>8338</v>
       </c>
       <c r="G873" t="n">
-        <v>8531.4</v>
+        <v>8423.799999999999</v>
       </c>
       <c r="H873" t="n">
-        <v>239709047800</v>
+        <v>23970904.78</v>
       </c>
       <c r="I873" t="n">
         <v>142245</v>
@@ -29253,7 +29253,7 @@
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -29272,16 +29272,49 @@
         <v>8479.4</v>
       </c>
       <c r="F874" t="n">
-        <v>8110.2</v>
+        <v>8105.6</v>
       </c>
       <c r="G874" t="n">
-        <v>8423.799999999999</v>
+        <v>8129.4</v>
       </c>
       <c r="H874" t="n">
-        <v>271218487200</v>
+        <v>29703099.184</v>
       </c>
       <c r="I874" t="n">
-        <v>164108</v>
+        <v>179978</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>0</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>IMZL.CFE</t>
+        </is>
+      </c>
+      <c r="D875" t="n">
+        <v>8076.2</v>
+      </c>
+      <c r="E875" t="n">
+        <v>8225.200000000001</v>
+      </c>
+      <c r="F875" t="n">
+        <v>8043.2</v>
+      </c>
+      <c r="G875" t="n">
+        <v>8110</v>
+      </c>
+      <c r="H875" t="n">
+        <v>194815231240</v>
+      </c>
+      <c r="I875" t="n">
+        <v>119806</v>
       </c>
     </row>
   </sheetData>
